--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4281,6 +4281,248 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120308039</v>
+      </c>
+      <c r="B33" t="n">
+        <v>104970</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>340</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>736697</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6411673</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Upptäckt av Johan Forsberg.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Sandkulle mellan våtmark och hygge.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120308041</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97800</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>290</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Röd skogslilja</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cephalanthera rubra</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle 1:11 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>736860</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6411923</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -4283,10 +4283,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308039</v>
+        <v>120308041</v>
       </c>
       <c r="B33" t="n">
-        <v>104970</v>
+        <v>97823</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,25 +4295,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4326,19 +4326,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736697</v>
+        <v>736860</v>
       </c>
       <c r="R33" t="n">
-        <v>6411673</v>
+        <v>6411923</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4370,11 +4375,6 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Upptäckt av Johan Forsberg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Sandkulle mellan våtmark och hygge.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308041</v>
+        <v>120308039</v>
       </c>
       <c r="B34" t="n">
-        <v>97800</v>
+        <v>104993</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4447,24 +4447,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736860</v>
+        <v>736697</v>
       </c>
       <c r="R34" t="n">
-        <v>6411923</v>
+        <v>6411673</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4496,6 +4491,11 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Upptäckt av Johan Forsberg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Sandkulle mellan våtmark och hygge.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -4283,10 +4283,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308041</v>
+        <v>120308039</v>
       </c>
       <c r="B33" t="n">
-        <v>97823</v>
+        <v>104993</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,25 +4295,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4326,24 +4326,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736860</v>
+        <v>736697</v>
       </c>
       <c r="R33" t="n">
-        <v>6411923</v>
+        <v>6411673</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4375,6 +4370,11 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Upptäckt av Johan Forsberg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Sandkulle mellan våtmark och hygge.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308039</v>
+        <v>120308041</v>
       </c>
       <c r="B34" t="n">
-        <v>104993</v>
+        <v>97823</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4447,19 +4447,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736697</v>
+        <v>736860</v>
       </c>
       <c r="R34" t="n">
-        <v>6411673</v>
+        <v>6411923</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4491,11 +4496,6 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Upptäckt av Johan Forsberg.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Sandkulle mellan våtmark och hygge.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -4283,10 +4283,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308039</v>
+        <v>120308041</v>
       </c>
       <c r="B33" t="n">
-        <v>104993</v>
+        <v>97823</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,25 +4295,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4326,19 +4326,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736697</v>
+        <v>736860</v>
       </c>
       <c r="R33" t="n">
-        <v>6411673</v>
+        <v>6411923</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4370,11 +4375,6 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Upptäckt av Johan Forsberg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Sandkulle mellan våtmark och hygge.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308041</v>
+        <v>120308039</v>
       </c>
       <c r="B34" t="n">
-        <v>97823</v>
+        <v>104993</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4447,24 +4447,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736860</v>
+        <v>736697</v>
       </c>
       <c r="R34" t="n">
-        <v>6411923</v>
+        <v>6411673</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4496,6 +4491,11 @@
           <t>2024-07-06</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Upptäckt av Johan Forsberg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Sandkulle mellan våtmark och hygge.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,12 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>108208</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3732,10 +3727,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>737094.3393965802</v>
+        <v>737094</v>
       </c>
       <c r="R28" t="n">
-        <v>6411586.502356729</v>
+        <v>6411587</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3765,19 +3760,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110696</v>
+        <v>110705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110705</v>
+        <v>110718</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110718</v>
+        <v>110727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110727</v>
+        <v>110732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110732</v>
+        <v>110760</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110760</v>
+        <v>110766</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110766</v>
+        <v>110773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110773</v>
+        <v>110777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110777</v>
+        <v>110785</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110788</v>
+        <v>110793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -3695,7 +3695,7 @@
         <v>106393020</v>
       </c>
       <c r="B28" t="n">
-        <v>110793</v>
+        <v>110801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104320524</v>
+        <v>120308041</v>
       </c>
       <c r="B2" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5747</v>
+        <v>290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Röd skogslilja</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cephalanthera rubra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>736662.834304498</v>
+        <v>736860</v>
       </c>
       <c r="R2" t="n">
-        <v>6411830.42913211</v>
+        <v>6411923</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,35 +770,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104320555</v>
+        <v>120308039</v>
       </c>
       <c r="B3" t="n">
-        <v>85148</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +802,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>433</v>
+        <v>340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>737091.8518599337</v>
+        <v>736697</v>
       </c>
       <c r="R3" t="n">
-        <v>6411728.520237975</v>
+        <v>6411673</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upptäckt av Johan Forsberg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,35 +886,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Sandkulle mellan våtmark och hygge.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104320531</v>
+        <v>104320500</v>
       </c>
       <c r="B4" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736735.6545729981</v>
+        <v>736741</v>
       </c>
       <c r="R4" t="n">
-        <v>6411839.52781748</v>
+        <v>6411785</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,19 +975,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104320537</v>
+        <v>104320516</v>
       </c>
       <c r="B5" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>736769.615787408</v>
+        <v>736625</v>
       </c>
       <c r="R5" t="n">
-        <v>6411817.479360093</v>
+        <v>6411841</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,19 +1076,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104320529</v>
+        <v>104320521</v>
       </c>
       <c r="B6" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>736726.2694579302</v>
+        <v>736658</v>
       </c>
       <c r="R6" t="n">
-        <v>6411835.234028183</v>
+        <v>6411836</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,19 +1177,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,39 +1210,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104320539</v>
+        <v>104320504</v>
       </c>
       <c r="B7" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1295,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736836.6608938347</v>
+        <v>737092</v>
       </c>
       <c r="R7" t="n">
-        <v>6411842.806842441</v>
+        <v>6411563</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,19 +1274,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104320530</v>
+        <v>104320555</v>
       </c>
       <c r="B8" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,23 +1318,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1411,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736733.2378495472</v>
+        <v>737092</v>
       </c>
       <c r="R8" t="n">
-        <v>6411844.195261929</v>
+        <v>6411729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,19 +1371,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1404,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104320554</v>
+        <v>104320497</v>
       </c>
       <c r="B9" t="n">
-        <v>85244</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6037417</v>
+        <v>442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulfotad denisespindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A.Ortega, Vila &amp; Fern.-Brime</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>737096.5600987532</v>
+        <v>737092</v>
       </c>
       <c r="R9" t="n">
-        <v>6411730.401322375</v>
+        <v>6411563</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,28 +1472,17 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1604,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104320511</v>
+        <v>104320502</v>
       </c>
       <c r="B10" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736799.0573979882</v>
+        <v>736724</v>
       </c>
       <c r="R10" t="n">
-        <v>6411790.354842135</v>
+        <v>6411786</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1677,19 +1573,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,15 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104320525</v>
+        <v>104320507</v>
       </c>
       <c r="B11" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,12 +1626,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1760,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736662.834304498</v>
+        <v>736961</v>
       </c>
       <c r="R11" t="n">
-        <v>6411830.42913211</v>
+        <v>6411712</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1793,19 +1674,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,15 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104320536</v>
+        <v>104320522</v>
       </c>
       <c r="B12" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,12 +1727,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1876,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736761.8318806528</v>
+        <v>736658</v>
       </c>
       <c r="R12" t="n">
-        <v>6411831.450272996</v>
+        <v>6411836</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1909,19 +1775,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,15 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104320534</v>
+        <v>104320525</v>
       </c>
       <c r="B13" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,21 +1819,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1992,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736744.2234643467</v>
+        <v>736663</v>
       </c>
       <c r="R13" t="n">
-        <v>6411839.498162159</v>
+        <v>6411831</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,19 +1876,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,15 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104320526</v>
+        <v>104320531</v>
       </c>
       <c r="B14" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2084,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2108,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736658.7227935687</v>
+        <v>736735</v>
       </c>
       <c r="R14" t="n">
-        <v>6411836.600084321</v>
+        <v>6411839</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,19 +1977,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,37 +2010,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104320509</v>
+        <v>104320536</v>
       </c>
       <c r="B15" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2224,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736908.5718722524</v>
+        <v>736761</v>
       </c>
       <c r="R15" t="n">
-        <v>6411740.158849667</v>
+        <v>6411832</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2257,19 +2078,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,15 +2111,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104320507</v>
+        <v>104320537</v>
       </c>
       <c r="B16" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,12 +2131,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2340,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736961.0859549793</v>
+        <v>736770</v>
       </c>
       <c r="R16" t="n">
-        <v>6411712.25711212</v>
+        <v>6411818</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2373,19 +2179,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,12 +2215,7 @@
         <v>104320556</v>
       </c>
       <c r="B17" t="n">
-        <v>85265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>737110.3104718525</v>
+        <v>737110</v>
       </c>
       <c r="R17" t="n">
-        <v>6411697.007960049</v>
+        <v>6411697</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2489,19 +2280,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,37 +2313,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104320514</v>
+        <v>104320509</v>
       </c>
       <c r="B18" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2572,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736724.3217724131</v>
+        <v>736909</v>
       </c>
       <c r="R18" t="n">
-        <v>6411786.486494936</v>
+        <v>6411740</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2605,19 +2381,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,15 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104320516</v>
+        <v>104320524</v>
       </c>
       <c r="B19" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>424</v>
+        <v>5747</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2688,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736625.2636078811</v>
+        <v>736663</v>
       </c>
       <c r="R19" t="n">
-        <v>6411841.042974306</v>
+        <v>6411831</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2721,19 +2482,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,50 +2515,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104320551</v>
+        <v>116686278</v>
       </c>
       <c r="B20" t="n">
-        <v>85163</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>248930</v>
+        <v>219677</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallkejsarspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius cedretorum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Maire</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>737108.8645613249</v>
+        <v>736642</v>
       </c>
       <c r="R20" t="n">
-        <v>6411730.592779431</v>
+        <v>6411781</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2834,22 +2580,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,70 +2601,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gamma, på död tall.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104320498</v>
+        <v>116686279</v>
       </c>
       <c r="B21" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003295</v>
+        <v>219677</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736961.0859549793</v>
+        <v>736727</v>
       </c>
       <c r="R21" t="n">
-        <v>6411712.25711212</v>
+        <v>6411836</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2950,22 +2687,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,73 +2703,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal med kjolgranar och grov tall. På tall och gran.</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104320528</v>
+        <v>116686284</v>
       </c>
       <c r="B22" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248956</v>
+        <v>219677</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736719.4265131942</v>
+        <v>736932</v>
       </c>
       <c r="R22" t="n">
-        <v>6411824.142482149</v>
+        <v>6411769</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3066,22 +2789,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,73 +2805,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal med kjolgranar och grov tall på relikta strandvallar av kalkgrus.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104320522</v>
+        <v>106393020</v>
       </c>
       <c r="B23" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>449</v>
+        <v>219719</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) W. D. J. Koch</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Lergrav 600-750 m S, Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736658.7227935687</v>
+        <v>737094</v>
       </c>
       <c r="R23" t="n">
-        <v>6411836.600084321</v>
+        <v>6411587</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3182,22 +2891,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1992-12-31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>. (Kordinat till - 149326) rikligt (koord = sydkant) Stora Valle 1:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,66 +2916,75 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
+          <t>Ingrid Engqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+          <t>Projekt Gotlands Flora</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104320502</v>
+        <v>116686274</v>
       </c>
       <c r="B24" t="n">
-        <v>85194</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>449</v>
+        <v>219862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736724.3217724131</v>
+        <v>736516</v>
       </c>
       <c r="R24" t="n">
-        <v>6411786.486494936</v>
+        <v>6411821</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3298,22 +3011,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,70 +3027,80 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104320521</v>
+        <v>116686275</v>
       </c>
       <c r="B25" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>424</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736658.7227935687</v>
+        <v>736528</v>
       </c>
       <c r="R25" t="n">
-        <v>6411836.600084321</v>
+        <v>6411821</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3414,22 +3127,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,70 +3143,80 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104320527</v>
+        <v>116686276</v>
       </c>
       <c r="B26" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248956</v>
+        <v>219862</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736662.834304498</v>
+        <v>736521</v>
       </c>
       <c r="R26" t="n">
-        <v>6411830.42913211</v>
+        <v>6411821</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3530,22 +3243,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,70 +3259,80 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104320505</v>
+        <v>116686277</v>
       </c>
       <c r="B27" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>248956</v>
+        <v>219862</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>737089.8480279215</v>
+        <v>736552</v>
       </c>
       <c r="R27" t="n">
-        <v>6411635.407691416</v>
+        <v>6411815</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3646,22 +3359,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,68 +3375,69 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106393020</v>
+        <v>116686283</v>
       </c>
       <c r="B28" t="n">
-        <v>110801</v>
+        <v>101326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219719</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Säfferot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Seseli libanotis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) W. D. J. Koch</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lergrav 600-750 m S, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>737094</v>
+        <v>736932</v>
       </c>
       <c r="R28" t="n">
-        <v>6411587</v>
+        <v>6411769</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3757,17 +3461,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>. (Kordinat till - 149326) rikligt (koord = sydkant) Stora Valle 1:11</t>
+          <t>2024-04-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,6 +3477,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gammal med kjolgranar och grov tall på relikta strandvallar av kalkgrus.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3787,75 +3491,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ingrid Engqvist</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116686274</v>
+        <v>104320551</v>
       </c>
       <c r="B29" t="n">
-        <v>97795</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219862</v>
+        <v>248930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tallkejsarspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius cedretorum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Maire</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736516</v>
+        <v>737109</v>
       </c>
       <c r="R29" t="n">
-        <v>6411821</v>
+        <v>6411731</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3882,12 +3563,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3898,71 +3579,65 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gammal.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116686279</v>
+        <v>104320505</v>
       </c>
       <c r="B30" t="n">
-        <v>109668</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219677</v>
+        <v>248956</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736727</v>
+        <v>737090</v>
       </c>
       <c r="R30" t="n">
-        <v>6411836</v>
+        <v>6411636</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3989,12 +3664,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,85 +3680,65 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gammal med kjolgranar och grov tall. På tall och gran.</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116686276</v>
+        <v>104320511</v>
       </c>
       <c r="B31" t="n">
-        <v>97795</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219862</v>
+        <v>248956</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736521</v>
+        <v>736799</v>
       </c>
       <c r="R31" t="n">
-        <v>6411821</v>
+        <v>6411790</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4110,12 +3765,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4126,85 +3781,65 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gammal.</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116686275</v>
+        <v>104320512</v>
       </c>
       <c r="B32" t="n">
-        <v>97795</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>248956</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) O-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736528</v>
+        <v>736741</v>
       </c>
       <c r="R32" t="n">
-        <v>6411821</v>
+        <v>6411785</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4231,12 +3866,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,83 +3882,68 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gammal.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120308039</v>
+        <v>104320514</v>
       </c>
       <c r="B33" t="n">
-        <v>105068</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>340</v>
+        <v>248956</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2), Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736697</v>
+        <v>736724</v>
       </c>
       <c r="R33" t="n">
-        <v>6411673</v>
+        <v>6411786</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4347,17 +3967,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Upptäckt av Johan Forsberg.</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4368,88 +3983,68 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Sandkulle mellan våtmark och hygge.</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120308041</v>
+        <v>104320526</v>
       </c>
       <c r="B34" t="n">
-        <v>97898</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>290</v>
+        <v>248956</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Röd skogslilja</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cephalanthera rubra</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2), Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736860</v>
+        <v>736658</v>
       </c>
       <c r="R34" t="n">
-        <v>6411923</v>
+        <v>6411836</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4473,12 +4068,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4489,24 +4084,832 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>104320527</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>736663</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6411831</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104320528</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>736720</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6411824</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>104320529</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>736727</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6411835</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>104320530</v>
+      </c>
+      <c r="B38" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>736734</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6411844</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>104320534</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>736745</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6411839</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>104320498</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>736961</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6411712</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104320539</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>736836</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6411842</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>104320554</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>737097</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6411731</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61697-2023 artfynd.xlsx
+++ b/artfynd/A 61697-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686274</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686275</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686277</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308041</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120308039</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,6 +1504,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320521</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320504</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320555</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320497</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320502</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2168,6 +2238,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320507</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2269,6 +2344,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320522</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320525</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320531</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320536</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2673,6 +2768,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320537</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320556</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2875,6 +2980,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320509</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2976,6 +3086,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320524</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686278</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3185,6 +3305,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686279</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,6 +3412,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686284</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3393,6 +3523,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106393020</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3495,6 +3630,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116686283</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3596,6 +3736,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320551</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3697,6 +3842,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320505</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3798,6 +3948,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320511</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3899,6 +4054,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320512</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4000,6 +4160,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320514</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4101,6 +4266,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320526</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4202,6 +4372,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320527</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4303,6 +4478,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4404,6 +4584,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320529</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4505,6 +4690,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320530</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4606,6 +4796,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320534</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4707,6 +4902,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320498</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4808,6 +5008,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320539</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4910,8 +5115,56 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320554</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>